--- a/mp-auth/src/main/resources/excel/import_template.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17020"/>
+    <workbookView windowHeight="16580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>: 1.</t>
     </r>
@@ -54,7 +54,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>,</t>
     </r>
@@ -70,7 +70,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>,</t>
     </r>
@@ -86,7 +86,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>,</t>
     </r>
@@ -102,7 +102,231 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>条数据</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>组织名请填写组织的路径，如：XX公司/市场部/销售组，角色名请填写角色的名称</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>如果填写了多个角色请用英文逗号分隔例如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"," ,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>如果在不填写这两个选项或未查询到组织或角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>则创建后用户的组织或角色为空</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>用户名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>姓名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>密码,角色必填，组织不填则默认一级组织</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>密码长度不低于6位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>且至少包含大小写字母，数字</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>用户名2-20个可见字符，不能和现有的重复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>姓名长度限制4-40个可见字符</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  7.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元格格式均为文本格式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>本文件前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t>100</t>
     </r>
@@ -112,29 +336,13 @@
         <rFont val="方正书宋_GBK"/>
         <charset val="134"/>
       </rPr>
-      <t>条数据</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">  2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
-      <t>组织名请填写组织的路径，如：XX公司/市场部/销售组，角色名请填写角色的名称</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
+      <t>行已修改为文本格式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t>,</t>
     </r>
@@ -144,221 +352,13 @@
         <rFont val="方正书宋_GBK"/>
         <charset val="134"/>
       </rPr>
-      <t>如果填写了多个角色请用英文逗号分隔例如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>"," ,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
-      <t>如果在不填写这两个选项或未查询到组织或角色</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
-      <t>则创建后用户的组织或角色为空</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">  3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
-      <t>用户名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
-      <t>姓名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
-      <t>密码,角色必填，组织不填则默认一级组织</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">  4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
-      <t>密码长度不低于6位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
-      <t>且至少包含大小写字母，数字</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">  5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
-      <t>用户名2-20个可见字符，不能和现有的重复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">  6.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
-      <t>姓名长度限制4-40个可见字符</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">  7.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元格格式均为文本格式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
-      <t>本文件前</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
-      <t>行已修改为文本格式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
       <t>注意，在内容填充后再修改单元格格式</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>,</t>
     </r>
@@ -377,12 +377,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -408,18 +408,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -438,6 +430,53 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -446,97 +485,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
@@ -551,6 +523,39 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -567,175 +572,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,46 +764,18 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -833,13 +810,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -852,151 +842,166 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/mp-auth/src/main/resources/excel/import_template.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16580"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7">
   <si>
     <t>用户名</t>
   </si>
@@ -31,6 +31,9 @@
     <t>角色</t>
   </si>
   <si>
+    <t>过期时间</t>
+  </si>
+  <si>
     <r>
       <t>说明</t>
     </r>
@@ -336,7 +339,7 @@
         <rFont val="方正书宋_GBK"/>
         <charset val="134"/>
       </rPr>
-      <t>行已修改为文本格式</t>
+      <t>行已修改为文本格式 注意，在内容填充后再修改单元格格式</t>
     </r>
     <r>
       <rPr>
@@ -352,23 +355,7 @@
         <rFont val="方正书宋_GBK"/>
         <charset val="134"/>
       </rPr>
-      <t>注意，在内容填充后再修改单元格格式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不会对已填充内容的格式产生影响</t>
+      <t>不会对已填充内容的格式产生影响  8. 过期时间格式为 yyyy-MM-dd HH:mm。</t>
     </r>
   </si>
 </sst>
@@ -378,11 +365,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -401,6 +388,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="方正书宋_GBK"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -409,14 +401,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -430,8 +453,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -439,39 +463,21 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -494,15 +500,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -516,37 +522,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -572,175 +564,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -764,18 +756,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -791,6 +772,39 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -827,189 +841,169 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1337,35 +1331,38 @@
     <col min="3" max="3" width="17.6428571428571" customWidth="1"/>
     <col min="4" max="4" width="29.5535714285714" customWidth="1"/>
     <col min="5" max="5" width="19.6964285714286" customWidth="1"/>
+    <col min="6" max="6" width="18.6428571428571" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3"/>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
+      <c r="A2" s="3" t="s">
+        <v>6</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/mp-auth/src/main/resources/excel/import_template.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8">
   <si>
     <t>用户名</t>
   </si>
@@ -31,10 +31,18 @@
     <t>角色</t>
   </si>
   <si>
-    <t>过期时间</t>
+    <t>过期日期</t>
   </si>
   <si>
-    <r>
+    <t>简介</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
       <t>说明</t>
     </r>
     <r>
@@ -355,7 +363,7 @@
         <rFont val="方正书宋_GBK"/>
         <charset val="134"/>
       </rPr>
-      <t>不会对已填充内容的格式产生影响  8. 过期时间格式为 yyyy-MM-dd HH:mm。</t>
+      <t>不会对已填充内容的格式产生影响  8. 过期时间格式为 yyyy-MM-dd。</t>
     </r>
   </si>
 </sst>
@@ -407,22 +415,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -442,6 +434,53 @@
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -454,23 +493,53 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -478,67 +547,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -564,31 +572,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -600,13 +680,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -618,127 +740,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -755,8 +763,26 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -778,17 +804,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -810,21 +829,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -839,161 +843,165 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1323,8 +1331,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="14.0625" customWidth="1"/>
     <col min="2" max="2" width="18.375" customWidth="1"/>
@@ -1332,9 +1340,10 @@
     <col min="4" max="4" width="29.5535714285714" customWidth="1"/>
     <col min="5" max="5" width="19.6964285714286" customWidth="1"/>
     <col min="6" max="6" width="18.6428571428571" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.0625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1353,10 +1362,13 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>

--- a/mp-auth/src/main/resources/excel/import_template.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowHeight="16960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>用户名</t>
   </si>
@@ -38,11 +38,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="方正书宋_GBK"/>
-        <charset val="134"/>
-      </rPr>
       <t>说明</t>
     </r>
     <r>
@@ -363,7 +358,7 @@
         <rFont val="方正书宋_GBK"/>
         <charset val="134"/>
       </rPr>
-      <t>不会对已填充内容的格式产生影响  8. 过期时间格式为 yyyy-MM-dd。</t>
+      <t>不会对已填充内容的格式产生影响  8. 过期时间格式为 yyyy-MM-dd  9.简介长度不能超过1000字</t>
     </r>
   </si>
 </sst>
@@ -372,10 +367,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -408,8 +403,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -422,49 +447,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -476,6 +471,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -484,69 +510,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -572,19 +567,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -596,157 +735,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -763,8 +758,47 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -778,10 +812,27 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -801,207 +852,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1329,7 +1324,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4" outlineLevelRow="1" outlineLevelCol="6"/>

--- a/mp-auth/src/main/resources/excel/import_template.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16600"/>
+    <workbookView windowHeight="15800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,8 +42,8 @@
 2.组织名请填写组织的路径，如：XX公司/市场部/销售组，角色名请填写角色的名称,如果填写了多个角色请用英文逗号分隔例如"," ,如果在不填写这两个选项或未查询到组织或角色, 则创建后用户的组织或角色为空  
 3.用户名,姓名,密码,角色必填，组织不填则默认一级组织  
 4.密码长度不低于6位,且至少包含大小写字母，数字  
-5.用户名2-20个可见字符，不能和现有的重复  
-6.姓名长度限制4-40个可见字符  
+5.用户名长度限制2-20个可见字符，不能和现有的重复  
+6.姓名长度限制2-20个可见字符  
 7.单元格格式均为文本格式, 本文件前100行已修改为文本格式 注意，在内容填充后再修改单元格格式,不会对已填充内容的格式产生影响  
 8.过期时间格式为 yyyy-MM-dd  
 9.简介长度限制1000个可见字符</t>
@@ -54,10 +54,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -84,15 +84,61 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -106,16 +152,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -123,54 +162,53 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -182,54 +220,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -244,25 +244,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -274,43 +406,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -328,103 +424,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,8 +441,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -452,15 +467,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -480,32 +486,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -525,6 +510,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -538,148 +538,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/mp-auth/src/main/resources/excel/import_template.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15800"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>用户名</t>
   </si>
@@ -29,6 +29,12 @@
   </si>
   <si>
     <t>角色</t>
+  </si>
+  <si>
+    <t>专业</t>
+  </si>
+  <si>
+    <t>学号</t>
   </si>
   <si>
     <t>过期日期</t>
@@ -52,12 +58,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -84,18 +90,33 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -107,40 +128,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -152,22 +152,67 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
@@ -176,60 +221,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,19 +256,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -274,61 +394,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -340,91 +418,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,15 +441,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -471,26 +468,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -506,6 +488,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -527,6 +524,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -538,148 +544,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -689,62 +695,62 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1013,20 +1019,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="14.0625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.0666666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.6428571428571" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5535714285714" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.6964285714286" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.6428571428571" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.0625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="17.6416666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.55" style="1" customWidth="1"/>
+    <col min="5" max="7" width="19.7" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.6416666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="18.0666666666667" style="1" customWidth="1"/>
+    <col min="10" max="16374" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1042,26 +1048,35 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
       <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/mp-auth/src/main/resources/excel/import_template.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15800"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
   <si>
     <t>说明: 
 1.不能修改表格前两行,不能修改工作表名称,从第三行开始填写用户数据,最大导入1000条数据  
-2.组织名请填写组织的路径，如：XX公司/市场部/销售组，角色名请填写角色的名称,如果填写了多个角色请用英文逗号分隔例如"," ,如果在不填写这两个选项或未查询到组织或角色, 则创建后用户的组织或角色为空  
+2.组织名请填写平台已有组织的路径，如：XX公司/市场部/销售组，角色名请填写平台已有角色的名称,如果填写了多个角色请用英文逗号分隔例如","  
 3.用户名,姓名,密码,角色必填，组织不填则默认一级组织  
 4.密码长度不低于6位,且至少包含大小写字母，数字  
 5.用户名长度限制2-20个可见字符，不能和现有的重复  
@@ -52,12 +52,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -84,18 +84,33 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -107,40 +122,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -152,22 +146,67 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
@@ -176,60 +215,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,19 +250,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -274,61 +388,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -340,91 +412,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,15 +435,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -471,26 +462,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -506,6 +482,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -527,6 +518,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -538,148 +538,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -689,62 +689,62 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1014,15 +1014,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.0625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.0666666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.6428571428571" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5535714285714" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.6964285714286" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.6428571428571" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.0625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6416666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.55" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.6416666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.0666666666667" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1042,7 +1042,7 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1050,7 +1050,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="3"/>

--- a/mp-auth/src/main/resources/excel/import_template.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15800"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
   <si>
     <t>说明: 
 1.不能修改表格前两行,不能修改工作表名称,从第三行开始填写用户数据,最大导入1000条数据  
-2.组织名请填写组织的路径，如：XX公司/市场部/销售组，角色名请填写角色的名称,如果填写了多个角色请用英文逗号分隔例如"," ,如果在不填写这两个选项或未查询到组织或角色, 则创建后用户的组织或角色为空  
+2.组织名请填写组织的路径，如：XX公司/市场部/销售组，角色名请填写角色的名称,如果填写了多个角色请用英文逗号分隔例如"," ,如果未查询到组织或角色，需要修改正确再重新导入全部数据
 3.用户名,姓名,密码,角色必填，组织不填则默认一级组织  
 4.密码长度不低于6位,且至少包含大小写字母，数字  
 5.用户名长度限制2-20个可见字符，不能和现有的重复  
@@ -52,12 +52,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -84,18 +84,33 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -107,40 +122,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -152,22 +146,67 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
@@ -176,60 +215,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,19 +250,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -274,61 +388,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -340,91 +412,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,15 +435,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -471,26 +462,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -506,6 +482,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -527,6 +518,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -538,148 +538,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -689,62 +689,62 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1014,15 +1014,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.0625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.0666666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.6428571428571" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5535714285714" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.6964285714286" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.6428571428571" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.0625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6416666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.55" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.6416666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.0666666666667" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1042,7 +1042,7 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1050,7 +1050,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="3"/>

--- a/mp-auth/src/main/resources/excel/import_template.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 3.用户名,姓名,密码,角色必填，组织不填则默认一级组织  
 4.密码长度不低于6位,且至少包含大小写字母，数字  
 5.用户名长度限制2-20个可见字符，不能和现有的重复  
-6.姓名长度限制2-20个可见字符  
+6.姓名长度限制4-40个可见字符  
 7.单元格格式均为文本格式, 本文件前100行已修改为文本格式 注意，在内容填充后再修改单元格格式,不会对已填充内容的格式产生影响  
 8.过期时间格式为 yyyy-MM-dd  
 9.简介长度限制1000个可见字符</t>

--- a/mp-auth/src/main/resources/excel/import_template.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template.xlsx
@@ -4,12 +4,25 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -19,7 +32,7 @@
     <t>用户名</t>
   </si>
   <si>
-    <t>姓名</t>
+    <t>别名</t>
   </si>
   <si>
     <t>密码</t>
@@ -52,7 +65,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>

--- a/mp-auth/src/main/resources/excel/import_template.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template.xlsx
@@ -32,7 +32,7 @@
     <t>用户名</t>
   </si>
   <si>
-    <t>别名</t>
+    <t>昵称</t>
   </si>
   <si>
     <t>密码</t>

--- a/mp-auth/src/main/resources/excel/import_template.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template.xlsx
@@ -53,10 +53,10 @@
     <t>说明: 
 1.不能修改表格前两行,不能修改工作表名称,从第三行开始填写用户数据,最大导入1000条数据  
 2.组织名请填写平台已有组织的路径，如：XX公司/市场部/销售组，角色名请填写平台已有角色的名称,如果填写了多个角色请用英文逗号分隔例如","  
-3.用户名,姓名,密码,角色必填，组织不填则默认一级组织  
+3.用户名,昵称,密码,角色必填，组织不填则默认一级组织  
 4.密码长度不低于6位,且至少包含大小写字母，数字  
 5.用户名长度限制2-20个可见字符，不能和现有的重复  
-6.姓名长度限制4-40个可见字符  
+6.昵称长度限制4-40个可见字符  
 7.单元格格式均为文本格式, 本文件前100行已修改为文本格式 注意，在内容填充后再修改单元格格式,不会对已填充内容的格式产生影响  
 8.过期时间格式为 yyyy-MM-dd  
 9.简介长度限制1000个可见字符</t>
@@ -1062,7 +1062,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" ht="168" customHeight="1" spans="1:6">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
